--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,848 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126361655</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91253</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>523800</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6447162</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126361610</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>523778</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6447148</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126361583</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>523754</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6447122</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126361201</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523748</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6446858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126361490</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523642</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447031</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126361257</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6446850</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126361535</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523726</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447054</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126361230</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ycke, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523730</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6446775</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126361201</v>
+        <v>126361490</v>
       </c>
       <c r="B6" t="n">
         <v>98352</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523748</v>
+        <v>523642</v>
       </c>
       <c r="R6" t="n">
-        <v>6446858</v>
+        <v>6447031</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126361490</v>
+        <v>126361201</v>
       </c>
       <c r="B7" t="n">
         <v>98352</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1256,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523642</v>
+        <v>523748</v>
       </c>
       <c r="R7" t="n">
-        <v>6447031</v>
+        <v>6446858</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,37 +1319,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126361257</v>
+        <v>126361535</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523707</v>
+        <v>523726</v>
       </c>
       <c r="R8" t="n">
-        <v>6446850</v>
+        <v>6447054</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,42 +1425,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361535</v>
+        <v>126361257</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523726</v>
+        <v>523707</v>
       </c>
       <c r="R9" t="n">
-        <v>6447054</v>
+        <v>6446850</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -1319,42 +1319,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126361535</v>
+        <v>126361257</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523726</v>
+        <v>523707</v>
       </c>
       <c r="R8" t="n">
-        <v>6447054</v>
+        <v>6446850</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,37 +1420,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361257</v>
+        <v>126361535</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523707</v>
+        <v>523726</v>
       </c>
       <c r="R9" t="n">
-        <v>6446850</v>
+        <v>6447054</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126361655</v>
       </c>
       <c r="B3" t="n">
-        <v>91253</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>126361610</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126361583</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126361490</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>126361201</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,37 +1319,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126361257</v>
+        <v>126361535</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523707</v>
+        <v>523726</v>
       </c>
       <c r="R8" t="n">
-        <v>6446850</v>
+        <v>6447054</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,42 +1425,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361535</v>
+        <v>126361257</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523726</v>
+        <v>523707</v>
       </c>
       <c r="R9" t="n">
-        <v>6447054</v>
+        <v>6446850</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>126361230</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -1319,42 +1319,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126361535</v>
+        <v>126361257</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523726</v>
+        <v>523707</v>
       </c>
       <c r="R8" t="n">
-        <v>6447054</v>
+        <v>6446850</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,37 +1420,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361257</v>
+        <v>126361535</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523707</v>
+        <v>523726</v>
       </c>
       <c r="R9" t="n">
-        <v>6446850</v>
+        <v>6447054</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 57634-2024 artfynd.xlsx
+++ b/artfynd/A 57634-2024 artfynd.xlsx
@@ -1319,37 +1319,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126361257</v>
+        <v>126361535</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523707</v>
+        <v>523726</v>
       </c>
       <c r="R8" t="n">
-        <v>6446850</v>
+        <v>6447054</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,42 +1425,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361535</v>
+        <v>126361257</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523726</v>
+        <v>523707</v>
       </c>
       <c r="R9" t="n">
-        <v>6447054</v>
+        <v>6446850</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
